--- a/SHIVAM_PROVISION_STORE_sale.xlsx
+++ b/SHIVAM_PROVISION_STORE_sale.xlsx
@@ -17,12 +17,13 @@
     <sheet name="radhey_dipartmental" r:id="rId11" sheetId="9"/>
     <sheet name="rasam_restaurent__brewbakes_cou" r:id="rId12" sheetId="10"/>
     <sheet name="state_bank_of_india" r:id="rId13" sheetId="11"/>
+    <sheet name="SuryaDhara_Dhaba" r:id="rId14" sheetId="12"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="10">
   <si>
     <t>S_NO</t>
   </si>
@@ -220,6 +221,48 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:J1"/>

--- a/SHIVAM_PROVISION_STORE_sale.xlsx
+++ b/SHIVAM_PROVISION_STORE_sale.xlsx
@@ -18,12 +18,13 @@
     <sheet name="rasam_restaurent__brewbakes_cou" r:id="rId12" sheetId="10"/>
     <sheet name="state_bank_of_india" r:id="rId13" sheetId="11"/>
     <sheet name="SuryaDhara_Dhaba" r:id="rId14" sheetId="12"/>
+    <sheet name="Pristine_Stores" r:id="rId15" sheetId="13"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="10">
   <si>
     <t>S_NO</t>
   </si>
@@ -263,6 +264,48 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:J1"/>
